--- a/data/trans_orig/P32C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451721</t>
+          <t>452411</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464547</t>
+          <t>464422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>156418</t>
+          <t>156477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>615033</t>
+          <t>614790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>630371</t>
+          <t>630090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>29667</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>12883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32052</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1030144</t>
+          <t>1028751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1048371</t>
+          <t>1047969</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>523740</t>
+          <t>522883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>531908</t>
+          <t>531902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1559284</t>
+          <t>1559960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1578124</t>
+          <t>1578453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13414</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15552</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>337093</t>
+          <t>336594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347761</t>
+          <t>347661</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188999</t>
+          <t>188620</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>529087</t>
+          <t>530133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>541020</t>
+          <t>540973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49733</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59731</t>
+          <t>57626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1830185</t>
+          <t>1830279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1855384</t>
+          <t>1854757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>878207</t>
+          <t>877575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>891055</t>
+          <t>891114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2714772</t>
+          <t>2716877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2743223</t>
+          <t>2742994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>488630</t>
+          <t>489233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501460</t>
+          <t>501522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>223310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>225369</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>714787</t>
+          <t>713841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>726537</t>
+          <t>726733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34704</t>
+          <t>33909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>37744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1161636</t>
+          <t>1162431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1182147</t>
+          <t>1181094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>583507</t>
+          <t>584586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591617</t>
+          <t>591626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1750353</t>
+          <t>1751213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1770877</t>
+          <t>1770960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308200</t>
+          <t>306716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322013</t>
+          <t>321315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>220438</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>222563</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>529214</t>
+          <t>529011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>544489</t>
+          <t>543886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29005</t>
+          <t>28732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>55954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31952</t>
+          <t>31445</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58113</t>
+          <t>58423</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1972904</t>
+          <t>1970619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1997568</t>
+          <t>1997841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1031376</t>
+          <t>1032149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1039548</t>
+          <t>1039552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3009009</t>
+          <t>3008699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3035170</t>
+          <t>3035677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22708</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>328860</t>
+          <t>329903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344720</t>
+          <t>344463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130552</t>
+          <t>130382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465571</t>
+          <t>463777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>480671</t>
+          <t>479881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29326</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1218561</t>
+          <t>1219108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1234809</t>
+          <t>1234771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>703493</t>
+          <t>702575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>712091</t>
+          <t>712013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1927079</t>
+          <t>1926589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1944546</t>
+          <t>1944705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365797</t>
+          <t>365768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>374610</t>
+          <t>374587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>273852</t>
+          <t>273141</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643322</t>
+          <t>642970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652333</t>
+          <t>652351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45149</t>
+          <t>44999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>12756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26884</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52659</t>
+          <t>52468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1925367</t>
+          <t>1925517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1948272</t>
+          <t>1948328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1114757</t>
+          <t>1115417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1125250</t>
+          <t>1126076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3046031</t>
+          <t>3046222</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3071806</t>
+          <t>3072082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15756</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>228201</t>
+          <t>229204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239327</t>
+          <t>239515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>294930</t>
+          <t>295767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>306126</t>
+          <t>305858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>971719</t>
+          <t>971530</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>981571</t>
+          <t>981860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>691243</t>
+          <t>691511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>707188</t>
+          <t>706931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1667651</t>
+          <t>1669106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1686241</t>
+          <t>1686443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>335775</t>
+          <t>336642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343390</t>
+          <t>343507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243689</t>
+          <t>243608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>582135</t>
+          <t>581959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>589293</t>
+          <t>589531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27723</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19897</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>39486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1545381</t>
+          <t>1545056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1560783</t>
+          <t>1560894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002780</t>
+          <t>1004134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1018907</t>
+          <t>1019146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2556940</t>
+          <t>2556294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2577111</t>
+          <t>2578075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23738</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452411</t>
+          <t>451785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464422</t>
+          <t>464533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>156477</t>
+          <t>156704</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>614790</t>
+          <t>614041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>630090</t>
+          <t>630104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29667</t>
+          <t>27454</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31376</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1028751</t>
+          <t>1030964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1047969</t>
+          <t>1048290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>522883</t>
+          <t>522842</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>531902</t>
+          <t>531900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1559960</t>
+          <t>1559587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1578453</t>
+          <t>1578110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14506</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>336594</t>
+          <t>336445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347661</t>
+          <t>347775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188620</t>
+          <t>188405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>530133</t>
+          <t>529444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>540973</t>
+          <t>541220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57626</t>
+          <t>57897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1830279</t>
+          <t>1831175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1854757</t>
+          <t>1855502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>877575</t>
+          <t>878416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>891114</t>
+          <t>890882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2716877</t>
+          <t>2716606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2742994</t>
+          <t>2743021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489233</t>
+          <t>487929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501522</t>
+          <t>501313</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713841</t>
+          <t>714890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>726733</t>
+          <t>727077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33909</t>
+          <t>34220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37744</t>
+          <t>37442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1162431</t>
+          <t>1162120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1181094</t>
+          <t>1180570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>584586</t>
+          <t>584508</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591626</t>
+          <t>592617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1751213</t>
+          <t>1751515</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1770960</t>
+          <t>1771518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>17295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306716</t>
+          <t>306820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321315</t>
+          <t>321277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>529011</t>
+          <t>528649</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543886</t>
+          <t>544520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28732</t>
+          <t>28473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55954</t>
+          <t>54336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31445</t>
+          <t>31776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58423</t>
+          <t>58196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1970619</t>
+          <t>1972237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1997841</t>
+          <t>1998100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1032149</t>
+          <t>1032399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1039552</t>
+          <t>1039557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3008699</t>
+          <t>3008926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3035677</t>
+          <t>3035346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>25489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>329903</t>
+          <t>328861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344463</t>
+          <t>344372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130382</t>
+          <t>130737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>463777</t>
+          <t>462638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>479881</t>
+          <t>479755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29816</t>
+          <t>29734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1219108</t>
+          <t>1219364</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1234771</t>
+          <t>1234928</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>702575</t>
+          <t>703568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>712013</t>
+          <t>712012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1926589</t>
+          <t>1926671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1944705</t>
+          <t>1944834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,82 +4640,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4995</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4922</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>10223</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5374</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>4922</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1807</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>11188</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365768</t>
+          <t>366078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>374587</t>
+          <t>374610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>273141</t>
+          <t>273520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642970</t>
+          <t>643935</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652351</t>
+          <t>652355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44999</t>
+          <t>45455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,49 +4983,49 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12749</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12756</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>36</t>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52468</t>
+          <t>51856</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1925517</t>
+          <t>1925061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1948328</t>
+          <t>1949181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,44 +5096,44 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1121963</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1115424</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1126072</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>98,87%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1121963</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1115417</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1126076</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3046222</t>
+          <t>3046834</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3072082</t>
+          <t>3071911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>234865</t>
+          <t>249294</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229204</t>
+          <t>242797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239515</t>
+          <t>253447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,27 +5685,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>74045</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>71854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>301344</t>
+          <t>323339</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>295767</t>
+          <t>316454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>305858</t>
+          <t>327631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>243957</t>
+          <t>258511</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>243957</t>
+          <t>258511</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243957</t>
+          <t>258511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>311290</t>
+          <t>333444</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>311290</t>
+          <t>333444</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>311290</t>
+          <t>333444</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24961</t>
+          <t>29644</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>978084</t>
+          <t>1038713</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>971530</t>
+          <t>1032700</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>981860</t>
+          <t>1042664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>701273</t>
+          <t>549146</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>691511</t>
+          <t>538009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>706931</t>
+          <t>554826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1679358</t>
+          <t>1587858</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1669106</t>
+          <t>1575420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1686443</t>
+          <t>1595053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>984893</t>
+          <t>1045736</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>984893</t>
+          <t>1045736</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>984893</t>
+          <t>1045736</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>709173</t>
+          <t>559328</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>709173</t>
+          <t>559328</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>709173</t>
+          <t>559328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1694067</t>
+          <t>1605064</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1694067</t>
+          <t>1605064</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1694067</t>
+          <t>1605064</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,102 +6223,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>9706</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2562</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3414</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>8464</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6336,102 +6336,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>341337</t>
+          <t>364385</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>336642</t>
+          <t>358270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343507</t>
+          <t>366510</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>269271</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>266769</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>269819</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>633657</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>628142</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>636414</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>245672</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>243608</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>246170</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>587009</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>581959</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>589531</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>246170</t>
+          <t>269819</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>246170</t>
+          <t>269819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>246170</t>
+          <t>269819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>590423</t>
+          <t>637848</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>590423</t>
+          <t>637848</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>590423</t>
+          <t>637848</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>28175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>22496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39486</t>
+          <t>44735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1554287</t>
+          <t>1652392</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1545056</t>
+          <t>1644101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1560894</t>
+          <t>1660462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1013425</t>
+          <t>892463</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1004134</t>
+          <t>881271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1019146</t>
+          <t>898866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2567711</t>
+          <t>2544855</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2556294</t>
+          <t>2531622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2578075</t>
+          <t>2553861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1573104</t>
+          <t>1672276</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1573104</t>
+          <t>1672276</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1573104</t>
+          <t>1672276</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1022677</t>
+          <t>904081</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1022677</t>
+          <t>904081</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1022677</t>
+          <t>904081</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2595780</t>
+          <t>2576357</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2595780</t>
+          <t>2576357</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2595780</t>
+          <t>2576357</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
